--- a/samples/vistra_liquidity.xlsx
+++ b/samples/vistra_liquidity.xlsx
@@ -5951,7 +5951,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="359" t="str">
-        <x:v>Balance sheet 2026-06-30. TTM 2025-07-01 to 2026-06-30. USD millions unless x or %.</x:v>
+        <x:v>Balance sheet 2026-06-30. TTM 2025-07-01 to 2026-06-30. USD millions, except ratios (x) and percentages (%).</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -6199,7 +6199,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="317" t="str">
-        <x:v>USD millions unless x or %. Fiscal year and later TTM both span twelve months and overlap.</x:v>
+        <x:v>USD millions, except ratios (x) and percentages (%). Fiscal year and later TTM both span twelve months and overlap.</x:v>
       </x:c>
       <x:c r="B3" s="333"/>
       <x:c r="C3" s="333"/>
@@ -9844,7 +9844,7 @@
         <x:v>c-1</x:v>
       </x:c>
       <x:c r="K2" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L2" s="460" t="n">
         <x:v>6</x:v>
@@ -9894,7 +9894,7 @@
         <x:v>c-1</x:v>
       </x:c>
       <x:c r="K3" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L3" s="460" t="n">
         <x:v>6</x:v>
@@ -9944,7 +9944,7 @@
         <x:v>c-1</x:v>
       </x:c>
       <x:c r="K4" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L4" s="460" t="n">
         <x:v>6</x:v>
@@ -9994,7 +9994,7 @@
         <x:v>c-1</x:v>
       </x:c>
       <x:c r="K5" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L5" s="460" t="n">
         <x:v>6</x:v>
@@ -10044,7 +10044,7 @@
         <x:v>c-1</x:v>
       </x:c>
       <x:c r="K6" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L6" s="460" t="n">
         <x:v>6</x:v>
@@ -10094,7 +10094,7 @@
         <x:v>c-1</x:v>
       </x:c>
       <x:c r="K7" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L7" s="460" t="n">
         <x:v>6</x:v>
@@ -10144,7 +10144,7 @@
         <x:v>c-1</x:v>
       </x:c>
       <x:c r="K8" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L8" s="460" t="n">
         <x:v>6</x:v>
@@ -10194,7 +10194,7 @@
         <x:v>c-1</x:v>
       </x:c>
       <x:c r="K9" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L9" s="460" t="n">
         <x:v>6</x:v>
@@ -10244,7 +10244,7 @@
         <x:v>c-1</x:v>
       </x:c>
       <x:c r="K10" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L10" s="460" t="n">
         <x:v>6</x:v>
@@ -10294,7 +10294,7 @@
         <x:v>c-1</x:v>
       </x:c>
       <x:c r="K11" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L11" s="460" t="n">
         <x:v>6</x:v>
@@ -10344,7 +10344,7 @@
         <x:v>c-1</x:v>
       </x:c>
       <x:c r="K12" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L12" s="460" t="n">
         <x:v>6</x:v>
@@ -10394,7 +10394,7 @@
         <x:v>c-1</x:v>
       </x:c>
       <x:c r="K13" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L13" s="460" t="n">
         <x:v>6</x:v>
@@ -10444,7 +10444,7 @@
         <x:v>c-1</x:v>
       </x:c>
       <x:c r="K14" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L14" s="460" t="n">
         <x:v>6</x:v>
@@ -10494,7 +10494,7 @@
         <x:v>c-1</x:v>
       </x:c>
       <x:c r="K15" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L15" s="460" t="n">
         <x:v>6</x:v>
@@ -10544,7 +10544,7 @@
         <x:v>c-1</x:v>
       </x:c>
       <x:c r="K16" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L16" s="460" t="n">
         <x:v>6</x:v>
@@ -10594,7 +10594,7 @@
         <x:v>c-1</x:v>
       </x:c>
       <x:c r="K17" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L17" s="460" t="n">
         <x:v>6</x:v>
@@ -10644,7 +10644,7 @@
         <x:v>c-1</x:v>
       </x:c>
       <x:c r="K18" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L18" s="460" t="n">
         <x:v>6</x:v>
@@ -10694,7 +10694,7 @@
         <x:v>c-1</x:v>
       </x:c>
       <x:c r="K19" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L19" s="460" t="n">
         <x:v>6</x:v>
@@ -10744,7 +10744,7 @@
         <x:v>c-1</x:v>
       </x:c>
       <x:c r="K20" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L20" s="460" t="n">
         <x:v>6</x:v>
@@ -10794,7 +10794,7 @@
         <x:v>c-1</x:v>
       </x:c>
       <x:c r="K21" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L21" s="460" t="n">
         <x:v>6</x:v>
@@ -10844,7 +10844,7 @@
         <x:v>c-1</x:v>
       </x:c>
       <x:c r="K22" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L22" s="460" t="n">
         <x:v>6</x:v>
@@ -10894,7 +10894,7 @@
         <x:v>c-1</x:v>
       </x:c>
       <x:c r="K23" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L23" s="460" t="n">
         <x:v>6</x:v>
@@ -10944,7 +10944,7 @@
         <x:v>c-1</x:v>
       </x:c>
       <x:c r="K24" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L24" s="460" t="n">
         <x:v>6</x:v>
@@ -10994,7 +10994,7 @@
         <x:v>c-1</x:v>
       </x:c>
       <x:c r="K25" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L25" s="460" t="n">
         <x:v>6</x:v>
@@ -11044,7 +11044,7 @@
         <x:v>c-1</x:v>
       </x:c>
       <x:c r="K26" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L26" s="460" t="n">
         <x:v>6</x:v>
@@ -11094,7 +11094,7 @@
         <x:v>c-1</x:v>
       </x:c>
       <x:c r="K27" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L27" s="460" t="n">
         <x:v>6</x:v>
@@ -11144,7 +11144,7 @@
         <x:v>c-1</x:v>
       </x:c>
       <x:c r="K28" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L28" s="460" t="n">
         <x:v>6</x:v>
@@ -11192,7 +11192,7 @@
         <x:v>c-9</x:v>
       </x:c>
       <x:c r="K29" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L29" s="460" t="n">
         <x:v>6</x:v>
@@ -11240,7 +11240,7 @@
         <x:v>c-8</x:v>
       </x:c>
       <x:c r="K30" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L30" s="460" t="n">
         <x:v>6</x:v>
@@ -11288,7 +11288,7 @@
         <x:v>c-8</x:v>
       </x:c>
       <x:c r="K31" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L31" s="460" t="n">
         <x:v>6</x:v>
@@ -11336,7 +11336,7 @@
         <x:v>c-8</x:v>
       </x:c>
       <x:c r="K32" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L32" s="460" t="n">
         <x:v>6</x:v>
@@ -11384,7 +11384,7 @@
         <x:v>c-8</x:v>
       </x:c>
       <x:c r="K33" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L33" s="460" t="n">
         <x:v>6</x:v>
@@ -11432,7 +11432,7 @@
         <x:v>c-8</x:v>
       </x:c>
       <x:c r="K34" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L34" s="460" t="n">
         <x:v>6</x:v>
@@ -11480,7 +11480,7 @@
         <x:v>c-8</x:v>
       </x:c>
       <x:c r="K35" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L35" s="460" t="n">
         <x:v>6</x:v>
@@ -11528,7 +11528,7 @@
         <x:v>c-8</x:v>
       </x:c>
       <x:c r="K36" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L36" s="460" t="n">
         <x:v>6</x:v>
@@ -11576,7 +11576,7 @@
         <x:v>c-8</x:v>
       </x:c>
       <x:c r="K37" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L37" s="460" t="n">
         <x:v>6</x:v>
@@ -11624,7 +11624,7 @@
         <x:v>c-8</x:v>
       </x:c>
       <x:c r="K38" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L38" s="460" t="n">
         <x:v>6</x:v>
@@ -11672,7 +11672,7 @@
         <x:v>c-8</x:v>
       </x:c>
       <x:c r="K39" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L39" s="460" t="n">
         <x:v>6</x:v>
@@ -11720,7 +11720,7 @@
         <x:v>c-8</x:v>
       </x:c>
       <x:c r="K40" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L40" s="460" t="n">
         <x:v>6</x:v>
@@ -11768,7 +11768,7 @@
         <x:v>c-590</x:v>
       </x:c>
       <x:c r="K41" s="448" t="str">
-        <x:v>[["us-gaap:LongtermDebtTypeAxis","vistra:ProjectLevelDebtMember"]]</x:v>
+        <x:v>us-gaap:LongtermDebtTypeAxis = vistra:ProjectLevelDebtMember</x:v>
       </x:c>
       <x:c r="L41" s="460" t="n">
         <x:v>6</x:v>
@@ -11816,7 +11816,7 @@
         <x:v>c-592</x:v>
       </x:c>
       <x:c r="K42" s="448" t="str">
-        <x:v>[["us-gaap:LongtermDebtTypeAxis","vistra:VistraOperationsDebtMember"]]</x:v>
+        <x:v>us-gaap:LongtermDebtTypeAxis = vistra:VistraOperationsDebtMember</x:v>
       </x:c>
       <x:c r="L42" s="460" t="n">
         <x:v>6</x:v>
@@ -11864,7 +11864,7 @@
         <x:v>c-598</x:v>
       </x:c>
       <x:c r="K43" s="448" t="str">
-        <x:v>[["us-gaap:LongtermDebtTypeAxis","us-gaap:BridgeLoanMember"],["us-gaap:DebtInstrumentAxis","vistra:BCOPCreditFacilitiesMember"]]</x:v>
+        <x:v>us-gaap:LongtermDebtTypeAxis = us-gaap:BridgeLoanMember; us-gaap:DebtInstrumentAxis = vistra:BCOPCreditFacilitiesMember</x:v>
       </x:c>
       <x:c r="L43" s="460" t="n">
         <x:v>6</x:v>
@@ -11912,7 +11912,7 @@
         <x:v>c-600</x:v>
       </x:c>
       <x:c r="K44" s="448" t="str">
-        <x:v>[["us-gaap:LongtermDebtTypeAxis","vistra:ConstructionAndTermLoansMember"],["us-gaap:DebtInstrumentAxis","vistra:BCOPCreditFacilitiesMember"]]</x:v>
+        <x:v>us-gaap:LongtermDebtTypeAxis = vistra:ConstructionAndTermLoansMember; us-gaap:DebtInstrumentAxis = vistra:BCOPCreditFacilitiesMember</x:v>
       </x:c>
       <x:c r="L44" s="460" t="n">
         <x:v>6</x:v>
@@ -11960,7 +11960,7 @@
         <x:v>c-685</x:v>
       </x:c>
       <x:c r="K45" s="448" t="str">
-        <x:v>[["us-gaap:LongtermDebtTypeAxis","us-gaap:ConstructionLoansMember"],["us-gaap:DebtInstrumentAxis","vistra:PulaskiMember"]]</x:v>
+        <x:v>us-gaap:LongtermDebtTypeAxis = us-gaap:ConstructionLoansMember; us-gaap:DebtInstrumentAxis = vistra:PulaskiMember</x:v>
       </x:c>
       <x:c r="L45" s="460" t="n">
         <x:v>6</x:v>
@@ -12008,7 +12008,7 @@
         <x:v>c-686</x:v>
       </x:c>
       <x:c r="K46" s="448" t="str">
-        <x:v>[["us-gaap:LongtermDebtTypeAxis","us-gaap:ConstructionLoansMember"],["us-gaap:DebtInstrumentAxis","vistra:CoffeenTermLoanMember"]]</x:v>
+        <x:v>us-gaap:LongtermDebtTypeAxis = us-gaap:ConstructionLoansMember; us-gaap:DebtInstrumentAxis = vistra:CoffeenTermLoanMember</x:v>
       </x:c>
       <x:c r="L46" s="460" t="n">
         <x:v>6</x:v>
@@ -12056,7 +12056,7 @@
         <x:v>c-664</x:v>
       </x:c>
       <x:c r="K47" s="448" t="str">
-        <x:v>[["us-gaap:LongtermDebtTypeAxis","us-gaap:RevolvingCreditFacilityMember"],["us-gaap:DebtInstrumentAxis","vistra:VistraZeroTermLoanBFacilityMember"]]</x:v>
+        <x:v>us-gaap:LongtermDebtTypeAxis = us-gaap:RevolvingCreditFacilityMember; us-gaap:DebtInstrumentAxis = vistra:VistraZeroTermLoanBFacilityMember</x:v>
       </x:c>
       <x:c r="L47" s="460" t="n">
         <x:v>6</x:v>
@@ -12104,7 +12104,7 @@
         <x:v>c-665</x:v>
       </x:c>
       <x:c r="K48" s="448" t="str">
-        <x:v>[["us-gaap:LongtermDebtTypeAxis","us-gaap:RevolvingCreditFacilityMember"],["us-gaap:DebtInstrumentAxis","vistra:TexasEnergyFundLoanMember"]]</x:v>
+        <x:v>us-gaap:LongtermDebtTypeAxis = us-gaap:RevolvingCreditFacilityMember; us-gaap:DebtInstrumentAxis = vistra:TexasEnergyFundLoanMember</x:v>
       </x:c>
       <x:c r="L48" s="460" t="n">
         <x:v>6</x:v>
@@ -12152,7 +12152,7 @@
         <x:v>c-729</x:v>
       </x:c>
       <x:c r="K49" s="448" t="str">
-        <x:v>[["srt:OwnershipAxis","vistra:VistraVisionMember"]]</x:v>
+        <x:v>srt:OwnershipAxis = vistra:VistraVisionMember</x:v>
       </x:c>
       <x:c r="L49" s="460" t="n">
         <x:v>6</x:v>
@@ -12200,7 +12200,7 @@
         <x:v>c-606</x:v>
       </x:c>
       <x:c r="K50" s="448" t="str">
-        <x:v>[["us-gaap:LongtermDebtTypeAxis","vistra:VistraOperationsSeniorNotesMember"],["us-gaap:DebtInstrumentAxis","vistra:A5.050SeniorNotesDue2026Member"]]</x:v>
+        <x:v>us-gaap:LongtermDebtTypeAxis = vistra:VistraOperationsSeniorNotesMember; us-gaap:DebtInstrumentAxis = vistra:A5.050SeniorNotesDue2026Member</x:v>
       </x:c>
       <x:c r="L50" s="460" t="n">
         <x:v>6</x:v>
@@ -12248,7 +12248,7 @@
         <x:v>c-608</x:v>
       </x:c>
       <x:c r="K51" s="448" t="str">
-        <x:v>[["us-gaap:LongtermDebtTypeAxis","vistra:VistraOperationsSeniorNotesMember"],["us-gaap:DebtInstrumentAxis","vistra:A3.700SeniorNotesDue2027Member"]]</x:v>
+        <x:v>us-gaap:LongtermDebtTypeAxis = vistra:VistraOperationsSeniorNotesMember; us-gaap:DebtInstrumentAxis = vistra:A3.700SeniorNotesDue2027Member</x:v>
       </x:c>
       <x:c r="L51" s="460" t="n">
         <x:v>6</x:v>
@@ -12296,7 +12296,7 @@
         <x:v>c-612</x:v>
       </x:c>
       <x:c r="K52" s="448" t="str">
-        <x:v>[["us-gaap:LongtermDebtTypeAxis","vistra:VistraOperationsSeniorNotesMember"],["us-gaap:DebtInstrumentAxis","vistra:A5.000SeniorNotesDue2027Member"]]</x:v>
+        <x:v>us-gaap:LongtermDebtTypeAxis = vistra:VistraOperationsSeniorNotesMember; us-gaap:DebtInstrumentAxis = vistra:A5.000SeniorNotesDue2027Member</x:v>
       </x:c>
       <x:c r="L52" s="460" t="n">
         <x:v>6</x:v>
@@ -12344,7 +12344,7 @@
         <x:v>c-701</x:v>
       </x:c>
       <x:c r="K53" s="448" t="str">
-        <x:v>[["us-gaap:LongtermDebtTypeAxis","us-gaap:LetterOfCreditMember"],["us-gaap:DebtInstrumentAxis","vistra:SecuredLetterOfCreditFacilitiesMember"],["dei:LegalEntityAxis","vistra:VistraOperationsCompanyLLCMember"]]</x:v>
+        <x:v>us-gaap:LongtermDebtTypeAxis = us-gaap:LetterOfCreditMember; us-gaap:DebtInstrumentAxis = vistra:SecuredLetterOfCreditFacilitiesMember; dei:LegalEntityAxis = vistra:VistraOperationsCompanyLLCMember</x:v>
       </x:c>
       <x:c r="L53" s="460" t="n">
         <x:v>9</x:v>
@@ -12392,7 +12392,7 @@
         <x:v>c-704</x:v>
       </x:c>
       <x:c r="K54" s="448" t="str">
-        <x:v>[["us-gaap:CreditFacilityAxis","us-gaap:LetterOfCreditMember"],["us-gaap:DebtInstrumentAxis","vistra:AlternateLetterOfCreditFacilityMember"]]</x:v>
+        <x:v>us-gaap:CreditFacilityAxis = us-gaap:LetterOfCreditMember; us-gaap:DebtInstrumentAxis = vistra:AlternateLetterOfCreditFacilityMember</x:v>
       </x:c>
       <x:c r="L54" s="460" t="n">
         <x:v>6</x:v>
@@ -12440,7 +12440,7 @@
         <x:v>c-970</x:v>
       </x:c>
       <x:c r="K55" s="448" t="str">
-        <x:v>[["us-gaap:GuaranteeObligationsByNatureAxis","us-gaap:FinancialStandbyLetterOfCreditMember"],["dei:LegalEntityAxis","vistra:VistraOperationsCompanyLLCMember"]]</x:v>
+        <x:v>us-gaap:GuaranteeObligationsByNatureAxis = us-gaap:FinancialStandbyLetterOfCreditMember; dei:LegalEntityAxis = vistra:VistraOperationsCompanyLLCMember</x:v>
       </x:c>
       <x:c r="L55" s="460" t="n">
         <x:v>9</x:v>
@@ -12488,7 +12488,7 @@
         <x:v>c-660</x:v>
       </x:c>
       <x:c r="K56" s="448" t="str">
-        <x:v>[["us-gaap:LongtermDebtTypeAxis","us-gaap:LineOfCreditMember"],["us-gaap:DebtInstrumentAxis","vistra:SeniorSecuredRevolvingCreditFacilityMember"]]</x:v>
+        <x:v>us-gaap:LongtermDebtTypeAxis = us-gaap:LineOfCreditMember; us-gaap:DebtInstrumentAxis = vistra:SeniorSecuredRevolvingCreditFacilityMember</x:v>
       </x:c>
       <x:c r="L56" s="460" t="n">
         <x:v>6</x:v>
@@ -12536,7 +12536,7 @@
         <x:v>c-660</x:v>
       </x:c>
       <x:c r="K57" s="448" t="str">
-        <x:v>[["us-gaap:LongtermDebtTypeAxis","us-gaap:LineOfCreditMember"],["us-gaap:DebtInstrumentAxis","vistra:SeniorSecuredRevolvingCreditFacilityMember"]]</x:v>
+        <x:v>us-gaap:LongtermDebtTypeAxis = us-gaap:LineOfCreditMember; us-gaap:DebtInstrumentAxis = vistra:SeniorSecuredRevolvingCreditFacilityMember</x:v>
       </x:c>
       <x:c r="L57" s="460" t="n">
         <x:v>6</x:v>
@@ -12584,7 +12584,7 @@
         <x:v>c-660</x:v>
       </x:c>
       <x:c r="K58" s="448" t="str">
-        <x:v>[["us-gaap:LongtermDebtTypeAxis","us-gaap:LineOfCreditMember"],["us-gaap:DebtInstrumentAxis","vistra:SeniorSecuredRevolvingCreditFacilityMember"]]</x:v>
+        <x:v>us-gaap:LongtermDebtTypeAxis = us-gaap:LineOfCreditMember; us-gaap:DebtInstrumentAxis = vistra:SeniorSecuredRevolvingCreditFacilityMember</x:v>
       </x:c>
       <x:c r="L58" s="460" t="n">
         <x:v>6</x:v>
@@ -12632,7 +12632,7 @@
         <x:v>c-660</x:v>
       </x:c>
       <x:c r="K59" s="448" t="str">
-        <x:v>[["us-gaap:LongtermDebtTypeAxis","us-gaap:LineOfCreditMember"],["us-gaap:DebtInstrumentAxis","vistra:SeniorSecuredRevolvingCreditFacilityMember"]]</x:v>
+        <x:v>us-gaap:LongtermDebtTypeAxis = us-gaap:LineOfCreditMember; us-gaap:DebtInstrumentAxis = vistra:SeniorSecuredRevolvingCreditFacilityMember</x:v>
       </x:c>
       <x:c r="L59" s="460" t="n">
         <x:v>6</x:v>
@@ -12680,7 +12680,7 @@
         <x:v>c-662</x:v>
       </x:c>
       <x:c r="K60" s="448" t="str">
-        <x:v>[["us-gaap:LongtermDebtTypeAxis","us-gaap:RevolvingCreditFacilityMember"],["us-gaap:DebtInstrumentAxis","vistra:SeniorSecuredCommodityLinkedRevolvingCreditFacilityMember"]]</x:v>
+        <x:v>us-gaap:LongtermDebtTypeAxis = us-gaap:RevolvingCreditFacilityMember; us-gaap:DebtInstrumentAxis = vistra:SeniorSecuredCommodityLinkedRevolvingCreditFacilityMember</x:v>
       </x:c>
       <x:c r="L60" s="460" t="n">
         <x:v>6</x:v>
@@ -12728,7 +12728,7 @@
         <x:v>c-662</x:v>
       </x:c>
       <x:c r="K61" s="448" t="str">
-        <x:v>[["us-gaap:LongtermDebtTypeAxis","us-gaap:RevolvingCreditFacilityMember"],["us-gaap:DebtInstrumentAxis","vistra:SeniorSecuredCommodityLinkedRevolvingCreditFacilityMember"]]</x:v>
+        <x:v>us-gaap:LongtermDebtTypeAxis = us-gaap:RevolvingCreditFacilityMember; us-gaap:DebtInstrumentAxis = vistra:SeniorSecuredCommodityLinkedRevolvingCreditFacilityMember</x:v>
       </x:c>
       <x:c r="L61" s="460" t="n">
         <x:v>6</x:v>
@@ -12776,7 +12776,7 @@
         <x:v>c-662</x:v>
       </x:c>
       <x:c r="K62" s="448" t="str">
-        <x:v>[["us-gaap:LongtermDebtTypeAxis","us-gaap:RevolvingCreditFacilityMember"],["us-gaap:DebtInstrumentAxis","vistra:SeniorSecuredCommodityLinkedRevolvingCreditFacilityMember"]]</x:v>
+        <x:v>us-gaap:LongtermDebtTypeAxis = us-gaap:RevolvingCreditFacilityMember; us-gaap:DebtInstrumentAxis = vistra:SeniorSecuredCommodityLinkedRevolvingCreditFacilityMember</x:v>
       </x:c>
       <x:c r="L62" s="460" t="n">
         <x:v>6</x:v>
@@ -12824,7 +12824,7 @@
         <x:v>c-662</x:v>
       </x:c>
       <x:c r="K63" s="448" t="str">
-        <x:v>[["us-gaap:LongtermDebtTypeAxis","us-gaap:RevolvingCreditFacilityMember"],["us-gaap:DebtInstrumentAxis","vistra:SeniorSecuredCommodityLinkedRevolvingCreditFacilityMember"]]</x:v>
+        <x:v>us-gaap:LongtermDebtTypeAxis = us-gaap:RevolvingCreditFacilityMember; us-gaap:DebtInstrumentAxis = vistra:SeniorSecuredCommodityLinkedRevolvingCreditFacilityMember</x:v>
       </x:c>
       <x:c r="L63" s="460" t="n">
         <x:v>6</x:v>
@@ -12872,7 +12872,7 @@
         <x:v>c-663</x:v>
       </x:c>
       <x:c r="K64" s="448" t="str">
-        <x:v>[["us-gaap:DebtInstrumentAxis","vistra:BCOPCreditFacilitiesMember"]]</x:v>
+        <x:v>us-gaap:DebtInstrumentAxis = vistra:BCOPCreditFacilitiesMember</x:v>
       </x:c>
       <x:c r="L64" s="460" t="n">
         <x:v>6</x:v>
@@ -12920,7 +12920,7 @@
         <x:v>c-664</x:v>
       </x:c>
       <x:c r="K65" s="448" t="str">
-        <x:v>[["us-gaap:LongtermDebtTypeAxis","us-gaap:RevolvingCreditFacilityMember"],["us-gaap:DebtInstrumentAxis","vistra:VistraZeroTermLoanBFacilityMember"]]</x:v>
+        <x:v>us-gaap:LongtermDebtTypeAxis = us-gaap:RevolvingCreditFacilityMember; us-gaap:DebtInstrumentAxis = vistra:VistraZeroTermLoanBFacilityMember</x:v>
       </x:c>
       <x:c r="L65" s="460" t="n">
         <x:v>6</x:v>
@@ -12968,7 +12968,7 @@
         <x:v>c-665</x:v>
       </x:c>
       <x:c r="K66" s="448" t="str">
-        <x:v>[["us-gaap:LongtermDebtTypeAxis","us-gaap:RevolvingCreditFacilityMember"],["us-gaap:DebtInstrumentAxis","vistra:TexasEnergyFundLoanMember"]]</x:v>
+        <x:v>us-gaap:LongtermDebtTypeAxis = us-gaap:RevolvingCreditFacilityMember; us-gaap:DebtInstrumentAxis = vistra:TexasEnergyFundLoanMember</x:v>
       </x:c>
       <x:c r="L66" s="460" t="n">
         <x:v>6</x:v>
@@ -13018,7 +13018,7 @@
         <x:v>c-510</x:v>
       </x:c>
       <x:c r="K67" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L67" s="460" t="n">
         <x:v>6</x:v>
@@ -13068,7 +13068,7 @@
         <x:v>c-510</x:v>
       </x:c>
       <x:c r="K68" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L68" s="460" t="n">
         <x:v>6</x:v>
@@ -13118,7 +13118,7 @@
         <x:v>c-91</x:v>
       </x:c>
       <x:c r="K69" s="448" t="str">
-        <x:v>[["us-gaap:BusinessAcquisitionAxis","vistra:CogentrixEnergyMember"]]</x:v>
+        <x:v>us-gaap:BusinessAcquisitionAxis = vistra:CogentrixEnergyMember</x:v>
       </x:c>
       <x:c r="L69" s="460" t="n">
         <x:v>9</x:v>
@@ -13166,7 +13166,7 @@
         <x:v>c-7</x:v>
       </x:c>
       <x:c r="K70" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L70" s="460" t="n">
         <x:v>6</x:v>
@@ -13214,7 +13214,7 @@
         <x:v>c-7</x:v>
       </x:c>
       <x:c r="K71" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L71" s="460" t="n">
         <x:v>6</x:v>
@@ -13262,7 +13262,7 @@
         <x:v>c-7</x:v>
       </x:c>
       <x:c r="K72" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L72" s="460" t="n">
         <x:v>6</x:v>
@@ -13310,7 +13310,7 @@
         <x:v>c-7</x:v>
       </x:c>
       <x:c r="K73" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L73" s="460" t="n">
         <x:v>6</x:v>
@@ -13358,7 +13358,7 @@
         <x:v>c-7</x:v>
       </x:c>
       <x:c r="K74" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L74" s="460" t="n">
         <x:v>6</x:v>
@@ -13406,7 +13406,7 @@
         <x:v>c-7</x:v>
       </x:c>
       <x:c r="K75" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L75" s="460" t="n">
         <x:v>6</x:v>
@@ -13454,7 +13454,7 @@
         <x:v>c-7</x:v>
       </x:c>
       <x:c r="K76" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L76" s="460" t="n">
         <x:v>6</x:v>
@@ -13502,7 +13502,7 @@
         <x:v>c-7</x:v>
       </x:c>
       <x:c r="K77" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L77" s="460" t="n">
         <x:v>6</x:v>
@@ -13552,7 +13552,7 @@
         <x:v>c-1</x:v>
       </x:c>
       <x:c r="K78" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L78" s="460" t="n">
         <x:v>6</x:v>
@@ -13606,7 +13606,7 @@
         <x:v>c-1</x:v>
       </x:c>
       <x:c r="K79" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L79" s="460" t="n">
         <x:v>6</x:v>
@@ -13660,7 +13660,7 @@
         <x:v>c-1</x:v>
       </x:c>
       <x:c r="K80" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L80" s="460" t="n">
         <x:v>6</x:v>
@@ -13714,7 +13714,7 @@
         <x:v>c-1</x:v>
       </x:c>
       <x:c r="K81" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L81" s="460" t="n">
         <x:v>6</x:v>
@@ -13768,7 +13768,7 @@
         <x:v>c-1</x:v>
       </x:c>
       <x:c r="K82" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L82" s="460" t="n">
         <x:v>6</x:v>
@@ -13822,7 +13822,7 @@
         <x:v>c-1</x:v>
       </x:c>
       <x:c r="K83" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L83" s="460" t="n">
         <x:v>6</x:v>
@@ -13876,7 +13876,7 @@
         <x:v>c-1</x:v>
       </x:c>
       <x:c r="K84" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L84" s="460" t="n">
         <x:v>6</x:v>
@@ -13930,7 +13930,7 @@
         <x:v>c-1</x:v>
       </x:c>
       <x:c r="K85" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L85" s="460" t="n">
         <x:v>6</x:v>
@@ -13984,7 +13984,7 @@
         <x:v>c-1</x:v>
       </x:c>
       <x:c r="K86" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L86" s="460" t="n">
         <x:v>6</x:v>
@@ -14038,7 +14038,7 @@
         <x:v>c-1</x:v>
       </x:c>
       <x:c r="K87" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L87" s="460" t="n">
         <x:v>6</x:v>
@@ -14092,7 +14092,7 @@
         <x:v>c-1</x:v>
       </x:c>
       <x:c r="K88" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L88" s="460" t="n">
         <x:v>6</x:v>
@@ -14146,7 +14146,7 @@
         <x:v>c-1</x:v>
       </x:c>
       <x:c r="K89" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L89" s="460" t="n">
         <x:v>6</x:v>
@@ -14200,7 +14200,7 @@
         <x:v>c-1</x:v>
       </x:c>
       <x:c r="K90" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L90" s="460" t="n">
         <x:v>6</x:v>
@@ -14254,7 +14254,7 @@
         <x:v>c-1</x:v>
       </x:c>
       <x:c r="K91" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L91" s="460" t="n">
         <x:v>6</x:v>
@@ -14308,7 +14308,7 @@
         <x:v>c-1</x:v>
       </x:c>
       <x:c r="K92" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L92" s="460" t="n">
         <x:v>6</x:v>
@@ -14362,7 +14362,7 @@
         <x:v>c-1</x:v>
       </x:c>
       <x:c r="K93" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L93" s="460" t="n">
         <x:v>6</x:v>
@@ -14416,7 +14416,7 @@
         <x:v>c-7</x:v>
       </x:c>
       <x:c r="K94" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L94" s="460" t="n">
         <x:v>6</x:v>
@@ -14470,7 +14470,7 @@
         <x:v>c-7</x:v>
       </x:c>
       <x:c r="K95" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L95" s="460" t="n">
         <x:v>6</x:v>
@@ -14524,7 +14524,7 @@
         <x:v>c-7</x:v>
       </x:c>
       <x:c r="K96" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L96" s="460" t="n">
         <x:v>6</x:v>
@@ -14578,7 +14578,7 @@
         <x:v>c-7</x:v>
       </x:c>
       <x:c r="K97" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L97" s="460" t="n">
         <x:v>6</x:v>
@@ -14632,7 +14632,7 @@
         <x:v>c-7</x:v>
       </x:c>
       <x:c r="K98" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L98" s="460" t="n">
         <x:v>6</x:v>
@@ -14686,7 +14686,7 @@
         <x:v>c-7</x:v>
       </x:c>
       <x:c r="K99" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L99" s="460" t="n">
         <x:v>6</x:v>
@@ -14740,7 +14740,7 @@
         <x:v>c-7</x:v>
       </x:c>
       <x:c r="K100" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L100" s="460" t="n">
         <x:v>6</x:v>
@@ -14794,7 +14794,7 @@
         <x:v>c-7</x:v>
       </x:c>
       <x:c r="K101" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L101" s="460" t="n">
         <x:v>6</x:v>
@@ -14848,7 +14848,7 @@
         <x:v>c-1</x:v>
       </x:c>
       <x:c r="K102" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L102" s="460" t="n">
         <x:v>6</x:v>
@@ -14902,7 +14902,7 @@
         <x:v>c-1</x:v>
       </x:c>
       <x:c r="K103" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L103" s="460" t="n">
         <x:v>6</x:v>
@@ -14956,7 +14956,7 @@
         <x:v>c-1</x:v>
       </x:c>
       <x:c r="K104" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L104" s="460" t="n">
         <x:v>6</x:v>
@@ -15010,7 +15010,7 @@
         <x:v>c-1</x:v>
       </x:c>
       <x:c r="K105" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L105" s="460" t="n">
         <x:v>6</x:v>
@@ -15064,7 +15064,7 @@
         <x:v>c-1</x:v>
       </x:c>
       <x:c r="K106" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L106" s="460" t="n">
         <x:v>6</x:v>
@@ -15118,7 +15118,7 @@
         <x:v>c-1</x:v>
       </x:c>
       <x:c r="K107" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L107" s="460" t="n">
         <x:v>6</x:v>
@@ -15172,7 +15172,7 @@
         <x:v>c-1</x:v>
       </x:c>
       <x:c r="K108" s="448" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L108" s="460" t="n">
         <x:v>6</x:v>
@@ -15226,7 +15226,7 @@
         <x:v>c-1</x:v>
       </x:c>
       <x:c r="K109" s="452" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L109" s="466" t="n">
         <x:v>6</x:v>
@@ -15536,7 +15536,7 @@
       </x:c>
       <x:c r="J127" s="369"/>
       <x:c r="K127" s="337" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L127" s="369"/>
       <x:c r="M127" s="369"/>
@@ -15580,7 +15580,7 @@
       </x:c>
       <x:c r="J128" s="369"/>
       <x:c r="K128" s="337" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L128" s="369"/>
       <x:c r="M128" s="369"/>
@@ -15624,7 +15624,7 @@
       </x:c>
       <x:c r="J129" s="369"/>
       <x:c r="K129" s="337" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L129" s="369"/>
       <x:c r="M129" s="369"/>
@@ -15670,7 +15670,7 @@
         <x:v>c-8</x:v>
       </x:c>
       <x:c r="K130" s="337" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L130" s="474" t="n">
         <x:v>6</x:v>
@@ -15714,7 +15714,7 @@
       <x:c r="I131" s="369"/>
       <x:c r="J131" s="369"/>
       <x:c r="K131" s="337" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L131" s="369"/>
       <x:c r="M131" s="369"/>
@@ -15762,7 +15762,7 @@
         <x:v>c-7</x:v>
       </x:c>
       <x:c r="K132" s="337" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L132" s="474" t="n">
         <x:v>6</x:v>
@@ -15814,7 +15814,7 @@
         <x:v>c-7</x:v>
       </x:c>
       <x:c r="K133" s="337" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L133" s="474" t="n">
         <x:v>6</x:v>
@@ -15866,7 +15866,7 @@
         <x:v>c-7</x:v>
       </x:c>
       <x:c r="K134" s="337" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L134" s="474" t="n">
         <x:v>6</x:v>
@@ -15918,7 +15918,7 @@
         <x:v>c-7</x:v>
       </x:c>
       <x:c r="K135" s="337" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L135" s="474" t="n">
         <x:v>6</x:v>
@@ -15970,7 +15970,7 @@
         <x:v>c-7</x:v>
       </x:c>
       <x:c r="K136" s="337" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L136" s="474" t="n">
         <x:v>6</x:v>
@@ -16022,7 +16022,7 @@
         <x:v>c-7</x:v>
       </x:c>
       <x:c r="K137" s="337" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L137" s="474" t="n">
         <x:v>6</x:v>
@@ -16068,7 +16068,7 @@
       <x:c r="I138" s="370"/>
       <x:c r="J138" s="370"/>
       <x:c r="K138" s="470" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L138" s="370"/>
       <x:c r="M138" s="370"/>
@@ -16170,7 +16170,7 @@
       </x:c>
       <x:c r="J142" s="369"/>
       <x:c r="K142" s="337" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L142" s="369"/>
       <x:c r="M142" s="369"/>
@@ -16216,7 +16216,7 @@
       </x:c>
       <x:c r="J143" s="369"/>
       <x:c r="K143" s="337" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L143" s="369"/>
       <x:c r="M143" s="369"/>
@@ -16262,7 +16262,7 @@
       </x:c>
       <x:c r="J144" s="369"/>
       <x:c r="K144" s="337" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L144" s="369"/>
       <x:c r="M144" s="369"/>
@@ -16308,7 +16308,7 @@
       </x:c>
       <x:c r="J145" s="369"/>
       <x:c r="K145" s="337" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L145" s="369"/>
       <x:c r="M145" s="369"/>
@@ -16356,7 +16356,7 @@
         <x:v>c-8</x:v>
       </x:c>
       <x:c r="K146" s="337" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L146" s="474" t="n">
         <x:v>6</x:v>
@@ -16406,7 +16406,7 @@
       </x:c>
       <x:c r="J147" s="369"/>
       <x:c r="K147" s="337" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L147" s="369"/>
       <x:c r="M147" s="369"/>
@@ -16452,7 +16452,7 @@
       </x:c>
       <x:c r="J148" s="369"/>
       <x:c r="K148" s="337" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L148" s="369"/>
       <x:c r="M148" s="369"/>
@@ -16502,7 +16502,7 @@
         <x:v>c-1</x:v>
       </x:c>
       <x:c r="K149" s="337" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L149" s="474" t="n">
         <x:v>6</x:v>
@@ -16556,7 +16556,7 @@
         <x:v>c-1</x:v>
       </x:c>
       <x:c r="K150" s="337" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L150" s="474" t="n">
         <x:v>6</x:v>
@@ -16610,7 +16610,7 @@
         <x:v>c-7</x:v>
       </x:c>
       <x:c r="K151" s="337" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L151" s="474" t="n">
         <x:v>6</x:v>
@@ -16664,7 +16664,7 @@
         <x:v>c-1</x:v>
       </x:c>
       <x:c r="K152" s="337" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L152" s="474" t="n">
         <x:v>6</x:v>
@@ -16718,7 +16718,7 @@
         <x:v>c-1</x:v>
       </x:c>
       <x:c r="K153" s="337" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L153" s="474" t="n">
         <x:v>6</x:v>
@@ -16772,7 +16772,7 @@
         <x:v>c-7</x:v>
       </x:c>
       <x:c r="K154" s="470" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L154" s="479" t="n">
         <x:v>6</x:v>
@@ -16880,7 +16880,7 @@
         <x:v>c-7</x:v>
       </x:c>
       <x:c r="K158" s="337" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L158" s="474" t="n">
         <x:v>6</x:v>
@@ -16934,7 +16934,7 @@
         <x:v>c-7</x:v>
       </x:c>
       <x:c r="K159" s="337" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L159" s="474" t="n">
         <x:v>6</x:v>
@@ -16988,7 +16988,7 @@
         <x:v>c-7</x:v>
       </x:c>
       <x:c r="K160" s="337" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L160" s="474" t="n">
         <x:v>6</x:v>
@@ -17044,7 +17044,7 @@
         <x:v>c-1</x:v>
       </x:c>
       <x:c r="K161" s="337" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L161" s="474" t="n">
         <x:v>6</x:v>
@@ -17098,7 +17098,7 @@
         <x:v>c-1</x:v>
       </x:c>
       <x:c r="K162" s="470" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="L162" s="479" t="n">
         <x:v>6</x:v>

--- a/samples/vistra_liquidity.xlsx
+++ b/samples/vistra_liquidity.xlsx
@@ -16552,6 +16552,674 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/drawings/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1100" b="1">
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1100" b="1">
+                <a:latin typeface="Arial"/>
+              </a:rPr>
+              <a:t>Fiscal-year-end cash and baseline borrowing (USD millions)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Annual history'!$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Cash and equivalents</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="3987E5"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Annual history'!$B$5:$F$5</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>FY2021</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>FY2022</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>FY2023</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>FY2024</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>FY2025</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Annual history'!$B$6:$F$6</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0,,;(#,##0,,)</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1325000000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>455000000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3485000000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1188000000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>785000000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Annual history'!$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Baseline borrowing</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="D95926"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Annual history'!$B$5:$F$5</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>FY2021</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>FY2022</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>FY2023</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>FY2024</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>FY2025</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Annual history'!$B$7:$F$7</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0,,;(#,##0,,)</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>10731000000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>13046000000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>14402000000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>17048000000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>20068000000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:gapWidth val="80"/>
+        <c:axId val="5001"/>
+        <c:axId val="5002"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="5001"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="low"/>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="0">
+                <a:latin typeface="Arial"/>
+                <a:cs typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="5002"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="5002"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="6350">
+              <a:solidFill>
+                <a:srgbClr val="D9D9D9"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" vert="horz"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1000">
+                    <a:latin typeface="Arial"/>
+                  </a:rPr>
+                  <a:t>USD millions</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="#,##0,,;(#,##0,,)" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="0">
+                <a:latin typeface="Arial"/>
+                <a:cs typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="5001"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1000" b="0">
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="1000" b="0">
+          <a:latin typeface="Arial"/>
+          <a:cs typeface="Arial"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1100" b="1">
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1100" b="1">
+                <a:latin typeface="Arial"/>
+              </a:rPr>
+              <a:t>Annual operating cash flow, capital spending (a use, below zero) and FCF (USD millions)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Annual history'!$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Operating cash flow</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="3987E5"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Annual history'!$B$5:$F$5</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>FY2021</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>FY2022</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>FY2023</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>FY2024</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>FY2025</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Annual history'!$B$8:$F$8</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0,,;(#,##0,,)</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>-206000000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>485000000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5453000000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4563000000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4070000000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Annual history'!$A$61</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Capital spending (a use of cash)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="7F838C"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Annual history'!$B$5:$F$5</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>FY2021</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>FY2022</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>FY2023</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>FY2024</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>FY2025</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Annual history'!$B$61:$F$61</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0,,;(#,##0,,)</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>-1033000000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-1301000000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-1676000000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-2078000000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-2752000000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Annual history'!$A$10</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Free cash flow</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="47627F"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Annual history'!$B$5:$F$5</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>FY2021</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>FY2022</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>FY2023</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>FY2024</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>FY2025</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Annual history'!$B$10:$F$10</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0,,;(#,##0,,)</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>-1239000000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-816000000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3777000000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2485000000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1318000000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:gapWidth val="80"/>
+        <c:axId val="5001"/>
+        <c:axId val="5002"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="5001"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="low"/>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="0">
+                <a:latin typeface="Arial"/>
+                <a:cs typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="5002"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="5002"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="6350">
+              <a:solidFill>
+                <a:srgbClr val="D9D9D9"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" vert="horz"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1000">
+                    <a:latin typeface="Arial"/>
+                  </a:rPr>
+                  <a:t>USD millions</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="#,##0,,;(#,##0,,)" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="0">
+                <a:latin typeface="Arial"/>
+                <a:cs typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="5001"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1000" b="0">
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="1000" b="0">
+          <a:latin typeface="Arial"/>
+          <a:cs typeface="Arial"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+</c:chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <xdr:twoCellAnchor>
@@ -16644,6 +17312,71 @@
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7d0dfa8075314111"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Annual chart 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="rIdAnnualBalances"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Annual chart 2"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="rIdAnnualFlows"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -17684,7 +18417,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
@@ -18003,8 +18736,39 @@
       <x:c r="F22" s="1014"/>
     </x:row>
     <x:row r="23" ht="21" customHeight="1"/>
+    <x:row r="60">
+      <x:c r="A60" s="1014" t="str">
+        <x:v>Chart data: capital spending as a use of cash, the negative of row 9 (missing years stay #N/A, so they leave a gap).</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" s="1035" t="str">
+        <x:v>Capital spending (a use of cash)</x:v>
+      </x:c>
+      <x:c r="B61" s="2021" t="n">
+        <x:f>IF(ISNUMBER(B9),-B9,NA())</x:f>
+        <x:v>-1033000000</x:v>
+      </x:c>
+      <x:c r="C61" s="2021" t="n">
+        <x:f>IF(ISNUMBER(C9),-C9,NA())</x:f>
+        <x:v>-1301000000</x:v>
+      </x:c>
+      <x:c r="D61" s="2021" t="n">
+        <x:f>IF(ISNUMBER(D9),-D9,NA())</x:f>
+        <x:v>-1676000000</x:v>
+      </x:c>
+      <x:c r="E61" s="2021" t="n">
+        <x:f>IF(ISNUMBER(E9),-E9,NA())</x:f>
+        <x:v>-2078000000</x:v>
+      </x:c>
+      <x:c r="F61" s="2022" t="n">
+        <x:f>IF(ISNUMBER(F9),-F9,NA())</x:f>
+        <x:v>-2752000000</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing r:id="rIdAnnualCharts"/>
 </x:worksheet>
 </file>
 
